--- a/inflearn/output/inflearn_main_2026-07-25.xlsx
+++ b/inflearn/output/inflearn_main_2026-07-25.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T07:04:57+09:00</t>
+          <t>2026-07-25T08:36:29+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T07:04:57+09:00</t>
+          <t>2026-07-25T08:36:29+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -781,7 +781,7 @@
         <v>6</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T07:04:57+09:00</t>
+          <t>2026-07-25T08:36:29+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T07:04:57+09:00</t>
+          <t>2026-07-25T08:36:29+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T07:04:57+09:00</t>
+          <t>2026-07-25T08:36:29+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T07:04:57+09:00</t>
+          <t>2026-07-25T08:36:29+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T07:04:57+09:00</t>
+          <t>2026-07-25T08:36:29+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T07:04:57+09:00</t>
+          <t>2026-07-25T08:36:29+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T07:04:57+09:00</t>
+          <t>2026-07-25T08:36:29+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T07:04:57+09:00</t>
+          <t>2026-07-25T08:36:29+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-25T07:04:57+09:00</t>
+          <t>2026-07-25T08:36:29+09:00</t>
         </is>
       </c>
     </row>

--- a/inflearn/output/inflearn_main_2026-07-25.xlsx
+++ b/inflearn/output/inflearn_main_2026-07-25.xlsx
@@ -11,7 +11,7 @@
     <sheet name="수집정보" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'강의목록'!$A$1:$R$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'강의목록'!$A$1:$R$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:36:29+09:00</t>
+          <t>2026-07-25T08:43:30+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:36:29+09:00</t>
+          <t>2026-07-25T08:43:30+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:36:29+09:00</t>
+          <t>2026-07-25T08:43:30+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:36:29+09:00</t>
+          <t>2026-07-25T08:43:30+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:36:29+09:00</t>
+          <t>2026-07-25T08:43:30+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:36:29+09:00</t>
+          <t>2026-07-25T08:43:30+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:36:29+09:00</t>
+          <t>2026-07-25T08:43:30+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:36:29+09:00</t>
+          <t>2026-07-25T08:43:30+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:36:29+09:00</t>
+          <t>2026-07-25T08:43:30+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:36:29+09:00</t>
+          <t>2026-07-25T08:43:30+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -1359,8 +1359,6842 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>이정환 Winterlood</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>74250</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>557</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>웹앱, 네트워크, 보안 교육, claude, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T13:27:12.011Z</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>컴공로드맵</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>89100</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>89100</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>202</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>1490</v>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>security, CPPG(개인정보관리사)</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>727</v>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>2023-11-16T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15T12:04:39.450Z</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>UI디자이너를 위한 언리얼 엔진 - 중급</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>루시</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>66000</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>게임 개발</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>게임 개발 기타, 게임 프로그래밍, 게임 아트 · 그래픽</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Unreal Engine, UE Blueprint, unreal-engine5, unreal-umg, Niagara</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>610</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T19:00:05.000Z</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:55:48.447Z</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/unreal-engine-for-ui</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>FlowCoder</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>2560</v>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>AI 활용(AX), AI 기술</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21T04:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-08T09:06:47.256Z</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>토비의 클린 스프링 - 도메인 모델 패턴과 헥사고날 아키텍처 Part 1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>토비</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>84700</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>121000</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>2429</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>백엔드</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Java, Spring, Spring Boot, JPA, hexagonal-architecture, 리팩터링, DDD</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>872</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-18T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-23T07:53:22.134Z</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/토비-클린스프링-도메인모델패턴-헥사고날-part1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Dante(곽지호)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>198000</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>198000</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>933</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>AI 기술, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, AI 실무 활용</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>1272</v>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-13T06:30:00.000Z</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23T13:58:42.615Z</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>AI 영상 제작 올인원: 이미지 생성부터 영상 편집까지</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>스탠리탬</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>11550</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>38500</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>AI 활용(AX), 디자인 · 아트</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>AI 시작하기, 사진 · 영상, AI 크리에이티브</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>영상제작, 콘텐츠 제작, Midjourney, 인공지능(AI), CapCut, ChatGPT</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:49:43.371Z</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T16:25:21.888Z</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/all-in-one-ai-video</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Java Champion Vlad Mihalcea 인터뷰</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Vlad Mihalcea</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>709</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>백엔드, AI 코딩, 커리어 · 자기계발 기타</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>Java, Spring, hibernate, spring-jpa, spring-data-jdbc</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14T05:56:00.000Z</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/vlad-mihalcea-interview</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>3020</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>56419</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Java, 객체지향</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>771</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-27T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-28T11:59:57.298Z</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>AI 지식 전달자</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>317</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>3488</v>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n"/>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-27T10:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-30T00:59:39.967Z</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>실용주의개발</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>88000</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>88000</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>1031</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>업무 생산성, wiki, obsidian, claude</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25T18:30:00.000Z</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T10:42:55.697Z</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>7996</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>122422</v>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>백엔드, 웹 개발</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>Java, Spring, MVC, Spring Boot</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>321</v>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>2020-07-19T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-30T11:34:33.353Z</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>일프로</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>61880</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>82500</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.2499393939393939</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>775</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>2765</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Kubernetes, devops, argocd, container, helm</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>669</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-11T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27T08:15:25.352Z</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>김영한의 실전 자바 - 기본편</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>44000</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>44000</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>2321</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>27750</v>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>Java, 객체지향</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>1012</v>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>2023-11-27T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>2025-12-23T06:52:23.926Z</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>[Rookiss] 클로드 코드 입문 (인터랙티브 교재)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Rookiss</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>69300</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>AI 기술, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, 인공지능 기타, AI 시작하기</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>인공지능(AI), claude, AX(에이전트 경험)</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T05:00:30.000Z</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T08:27:29.492Z</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/rookiss-introduction-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>실리콘밸리 엔지니어와 함께하는 Claude Code(개발자용)</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>미쿡엔지니어</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>44000</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>44000</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>181</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>2189</v>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, 개발 · 프로그래밍 기타, AI 실무 활용</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>업무 생산성, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>312</v>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09T07:04:40.343Z</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/claude-code-with-sil</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>AI 지식 전달자</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>596</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T04:00:06.000Z</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T07:01:04.312Z</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>38군데 합격 비법, 2026 코딩테스트 필수 알고리즘</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>딩코딩코</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>165000</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>165000</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>435</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>2782</v>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>알고리즘 · 자료구조, 취업 · 이직</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>Python, 코딩 테스트, 알고리즘, data-structure</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>934</v>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>2024-11-12T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-02T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/38군데-합격비법-코테-필수-알고리즘</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>챗봇을 만들며 배우는 ai agent 개발의 모든것(fastapi, RAG, vector, LangChain, sLLM/파인튜닝)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>bradkim</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>61600</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>88000</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>AI 기술, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, 인공지능 기타, AI 개발 활용</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>RAG, vector-database, FastAPI, LLM, Llama, Fine-Tuning, openAI API</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>507</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T06:30:06.000Z</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T07:03:29.747Z</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/everything-about-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>이정환 Winterlood</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>36300</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>48400</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>1511</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>15228</v>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>프론트엔드, 웹 개발</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>JavaScript, React, Node.js</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>1114</v>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>2022-01-26T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-13T00:57:34.805Z</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/한입-리액트</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>김영한의 실전 자바 - 중급 2편</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>66000</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>841</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>10654</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>1165</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-07T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-24T10:17:13.631Z</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>제어쟁이</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>385000</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>550000</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>498</v>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>임베디드 · IoT, 모빌리티</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>임베디드, stm32, hardware, motordriver, artwork</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>1017</v>
+      </c>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>2025-06-15T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05T13:30:17.886Z</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>김영한의 실전 자바 - 중급 1편</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>66000</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>1205</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>12152</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Java, 객체지향</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>1161</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-27T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-28T10:04:41.236Z</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>AI 에이전트 엔지니어링</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>민혁</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>1284</v>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>AI 기술, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>Python, 인공지능(AI), RAG, AI Agent</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="n">
+        <v>322</v>
+      </c>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-07T05:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-07T02:58:08.781Z</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>한 입 크기로 잘라먹는 Next.js</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>이정환 Winterlood</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>36300</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>48400</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>5792</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>프론트엔드, 웹 개발</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>React, TypeScript, Next.js</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>934</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-18T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T03:56:34.520Z</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/한입-크기-nextjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>비전공자도 이해할 수 있는 AWS 입문/실전</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>JSCODE 박재성</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>57750</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>77000</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>362</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>3240</v>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>데브옵스 · 인프라, 백엔드, 클라우드</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>AWS, aws-elb, aws-rds, ec2, s3</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>257</v>
+      </c>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>2023-11-29T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-11T05:28:03.130Z</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/비전공자-이해할수있는-aws-입문실전</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>RAG를 활용한 LLM Application 개발 (feat. LangChain)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>제이쓴</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>66000</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>4680</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>AI 기술, 개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, 개발 · 프로그래밍 기타</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>LLM, RAG, LangChain, vector-database, openAI API</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-27T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-15T11:12:24.826Z</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/rag-llm-application개발-langchain</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>미국 빅테크 프론트엔드 시스템 디자인 실전: 단순 구현자로 남지 않기 위한 프론트엔드 개발자를 위해</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>미국달팽이</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>74250</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>356</v>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>프론트엔드, AI 코딩, AI 개발 활용</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>frontend, 시스템 디자인, 인공지능(AI)</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>271</v>
+      </c>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27T02:26:00.000Z</t>
+        </is>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-24T10:26:38.868Z</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/us-big-tech-frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>깃미남의 Git 완전정복</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>깃미남 (깃에 미친 남자)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>59400</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>79200</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>개발 도구, 개발 · 프로그래밍 기타</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Git, GitHub, 버전관리시스템, github-actions, 협업</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T09:30:04.000Z</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T07:36:32.540Z</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/git-masterclass-by-g</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Certified Kubernetes Security Specialist (CKS) – Practical Exam Guide</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>일프로</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>66000</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>데브옵스 · 인프라, 시스템 · 운영체제, 보안 · 네트워크 자격증</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>Kubernetes, security, devops, infrastructure, container</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="n">
+        <v>259</v>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15T02:00:07.000Z</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13T08:31:14.489Z</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/certified-kubernetes-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>나도코딩</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>1878</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>39448</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>프로그래밍 언어</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>2020-02-24T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-29T06:34:34.311Z</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>675</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>10825</v>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="n">
+        <v>517</v>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>2025-07-31T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>2025-08-31T09:28:51.006Z</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>실전! 스프링 부트와 JPA 활용1 - 웹 애플리케이션 개발</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>88000</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>88000</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>2546</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>27505</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>백엔드, 웹 개발</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Java, Spring, 웹앱, Spring Boot, JPA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>464</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>2019-09-23T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-18T09:47:31.426Z</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/스프링부트-JPA-활용-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>생성형 AI의 작동 원리부터 나만의 AI Agent 개발까지 - 멀티모달, MCP, RAG, Agents SDK</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>YoungJea Oh</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>27500</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>Python, 딥러닝, 인공지능(AI), ChatGPT, 프롬프트엔지니어링, LLM, AI Agent</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="n">
+        <v>424</v>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-21T00:01:06.000Z</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-21T00:06:00.604Z</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/from-the-principles</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>인프런</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>33000</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>33000</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>1361</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>34118</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>프로그래밍 언어</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>857</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>2019-06-01T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-13T07:44:34.331Z</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>김영한의 실전 자바 - 고급 3편, 람다, 스트림, 함수형 프로그래밍</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>77000</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>77000</v>
+      </c>
+      <c r="F47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>334</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>5147</v>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>웹 개발, 프로그래밍 언어, 백엔드</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>Java, 함수형 프로그래밍, Lambda, optional</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="n">
+        <v>1001</v>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>2025-03-24T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>2025-09-14T05:27:02.800Z</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>채널톡 면접관이 직접 알려주는 CS 면접 대비 - 네트워크 &amp; 웹 편</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>JSCODE 제이온</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>53900</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>77000</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>취업 · 이직, 웹 개발, 개발 · 프로그래밍 기타</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>네트워크, websocket, https, dns, computer-science</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T10:00:07.000Z</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T05:13:07.132Z</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/cs-interview-prepara-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>김영한의 실전 자바 - 고급 1편, 멀티스레드와 동시성</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>77000</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>77000</v>
+      </c>
+      <c r="F49" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>576</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>9465</v>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>Java, 객체지향, thread, multithread, 동시성</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="n">
+        <v>1249</v>
+      </c>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t>2024-07-14T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-18T01:46:58.908Z</t>
+        </is>
+      </c>
+      <c r="Q49" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>[VOD] AI시대, 나의 전문성을 재설계하는 법</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>하용호</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>1019</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>AI 활용(AX), 커리어 · 자기계발</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>AI 실무 활용, 취업 · 이직, AI 시작하기</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T09:53:00.000Z</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26T00:21:35.186Z</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/ai시대-나의전문성-재설계-하는법</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>일프로</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F51" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>433</v>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>Kubernetes, devops, certificates, container</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="n">
+        <v>197</v>
+      </c>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-19T22:30:00.000Z</t>
+        </is>
+      </c>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-23T04:55:21.390Z</t>
+        </is>
+      </c>
+      <c r="Q51" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/certified-kubernetes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>AI 에이전트, 수익형 아키텍처 설계법</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>뉴노멀</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>19250</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>38500</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>AI 기술, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, AI 실무 활용, AI 시작하기</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Python, 인공지능(AI), AI Agent, 서비스 기획, LLM, claude, 면접</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T04:30:05.000Z</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15T11:23:15.183Z</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/ai-agents-how-to-des</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>AI 개발자 로드맵 2026</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>장철원</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>AI 기술</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, 딥러닝 · 머신러닝, 인공지능 기타</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>Python, 머신러닝, 딥러닝, 빅데이터, Docker, 인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23T08:00:05.000Z</t>
+        </is>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23T06:37:11.677Z</t>
+        </is>
+      </c>
+      <c r="Q53" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/ai-developer-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>김영한의 실전 자바 - 고급 2편, I/O, 네트워크, 리플렉션</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>77000</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>77000</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>6927</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Java, 네트워크, 객체지향</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>1296</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-06T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-08T10:29:28.205Z</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>최원영</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>1073</v>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>AI 기술, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>인공지능(AI)</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-27T05:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-27T06:18:36.692Z</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Qwen Conference 2026</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Alibaba Cloud</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>AI 활용(AX), 보안 · 네트워크, AI 기술</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>AI 개발 활용, 클라우드, AI에이전트 개발</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>QML, modeling, 원가절감, AI Agent, MCP</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>495</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10T06:30:06.000Z</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14T09:20:15.594Z</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/qwen-conference-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>옵시디언 마스터 클래스: PKM·AI Second Brain·LLM WiKi 기초부터 실전까지</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>조영수(데이먼)</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>132000</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>132000</v>
+      </c>
+      <c r="F57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>141</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>1001</v>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>업무 생산성, 기획 · 경영 · 마케팅, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>생산성 도구, 기획 · PM· PO, AI 실무 활용</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>업무 생산성, obsidian</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="n">
+        <v>455</v>
+      </c>
+      <c r="O57" s="7" t="inlineStr">
+        <is>
+          <t>2025-06-25T12:30:00.000Z</t>
+        </is>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-08T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Q57" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/옵시디언-마스터-클래스생산성을-바꾸는-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>LangGraph를 활용한 AI Agent 개발 (feat. MCP)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>제이쓴</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>69300</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>69300</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>2706</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>AI 기술</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>프롬프트엔지니어링, LLM, AI Agent, LangGraph, MCP</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-19T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T10:57:36.230Z</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/랭그래프-활용한-llm에이전트-개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>10주완성 C++ 코딩테스트 | 알고리즘 코딩테스트</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>큰돌</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>165000</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>165000</v>
+      </c>
+      <c r="F59" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>357</v>
+      </c>
+      <c r="I59" s="7" t="n">
+        <v>4995</v>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>알고리즘 · 자료구조, 프로그래밍 언어, 취업 · 이직</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>코딩 테스트, C++</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="n">
+        <v>1696</v>
+      </c>
+      <c r="O59" s="7" t="inlineStr">
+        <is>
+          <t>2021-12-22T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-01T12:08:18.990Z</t>
+        </is>
+      </c>
+      <c r="Q59" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/10주완성-코딩테스트-큰돌</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>강민철</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>20666</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>컴퓨터 구조, 운영체제, 기술면접</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>823</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>2023-03-02T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-29T09:43:24.787Z</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>실리콘밸리 엔지니어와 함께하는 Codex</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>미쿡엔지니어</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>44000</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>44000</v>
+      </c>
+      <c r="F61" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H61" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="7" t="n">
+        <v>663</v>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>AI 활용(AX), AI 기술</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>AI 실무 활용, AI 시작하기, AI에이전트 개발</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>인공지능(AI), Python, codex, claude, AI Agent, openai</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="n">
+        <v>204</v>
+      </c>
+      <c r="O61" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:59:36.048Z</t>
+        </is>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21T20:46:08.861Z</t>
+        </is>
+      </c>
+      <c r="Q61" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/codex-with-silicon-v</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>클로드 코드 완벽 가이드: AI 에이전트 제대로 활용하기</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Kyo</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>61600</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>88000</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>AI 활용(AX), 개발 · 프로그래밍, AI 기술</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>AI 개발 활용, 풀스택, AI에이전트 개발</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>AI Agent, claude, 바이브코딩, supabase, Next.js, AX(에이전트 경험), 인공지능(AI)</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T21:30:04.000Z</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:12:21.512Z</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/claude-code-ultimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>AWS Certified Solutions Architect - Associate 자격증 준비하기</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>코드바나나</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>148500</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>148500</v>
+      </c>
+      <c r="F63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H63" s="7" t="n">
+        <v>295</v>
+      </c>
+      <c r="I63" s="7" t="n">
+        <v>3635</v>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>데브옵스 · 인프라, 클라우드, 백엔드, 보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증</t>
+        </is>
+      </c>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t>AWS, 네트워크</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="n">
+        <v>1450</v>
+      </c>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t>2022-06-21T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:34:27.737Z</t>
+        </is>
+      </c>
+      <c r="Q63" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/aws-자격증-어소시에이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>김영한의 실전 데이터베이스 - 기본편</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>88000</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>88000</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>471</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>4851</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-31T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-16T03:54:43.001Z</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>시스코 CCNA 함께 공부해요</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>ccie_pe_kim</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>951</v>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>보안 · 네트워크</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
+        </is>
+      </c>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>네트워크, CCNA, routing, tcpip</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="n">
+        <v>1213</v>
+      </c>
+      <c r="O65" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-30T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-25T09:44:13.272Z</t>
+        </is>
+      </c>
+      <c r="Q65" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>코딩테스트 [ ALL IN ONE ]</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>개발남노씨</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>165000</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>165000</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>2631</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>알고리즘 · 자료구조, 프로그래밍 언어</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Python, 알고리즘, 코딩 테스트</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>1116</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>2022-12-21T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-13T07:42:34.757Z</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/코딩테스트-입문-파이썬</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>개발자 개념 장착 - 프로그래밍 개발에 필요한 필수 개념과 핵심 이론정리</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>코딩하는기술사</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I67" s="7" t="n">
+        <v>1006</v>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍 기타, 웹 개발, 백엔드</t>
+        </is>
+      </c>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t>아키텍처, 컴퓨터 구조, 기술면접, 소프트웨어 설계, 문제해결능력</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="n"/>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-19T13:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-30T22:11:57.790Z</t>
+        </is>
+      </c>
+      <c r="Q67" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/개발자-개념-장착-프로그래밍-개발에</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>확장성 있는 Flutter: Supabase, Clean Architecture &amp; Riverpod</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>조상욱</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>32670</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>108900</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>모바일 앱 개발, 풀스택, 데이터베이스</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Flutter, riverpod, clean-architecture, monorepo, supabase</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>1217</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T09:00:32.000Z</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10T06:09:52.285Z</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/scalable-flutter-sup</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>스프링 핵심 원리 - 기본편</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>88000</v>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>88000</v>
+      </c>
+      <c r="F69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>4885</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>50090</v>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>백엔드, 웹 개발</t>
+        </is>
+      </c>
+      <c r="M69" s="7" t="inlineStr">
+        <is>
+          <t>Spring, 객체지향</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="n">
+        <v>725</v>
+      </c>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
+          <t>2020-09-20T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>2025-06-04T15:00:00.555Z</t>
+        </is>
+      </c>
+      <c r="Q69" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code Harness Engineering 클로드코드 심화 CLI 하네스 엔지니어링 실무</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>미국달팽이</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>88000</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>88000</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>AI 개발 활용, 풀스택, AI 실무 활용</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>인공지능(AI), claude, 바이브코딩, 하네스</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24T22:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16T18:23:30.236Z</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/claude-code-harness</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>대세는 쿠버네티스 (초급~중급편)</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>일프로</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>33000</v>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>44000</v>
+      </c>
+      <c r="F71" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G71" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>611</v>
+      </c>
+      <c r="I71" s="7" t="n">
+        <v>8337</v>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+        </is>
+      </c>
+      <c r="M71" s="7" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
+        </is>
+      </c>
+      <c r="N71" s="7" t="n">
+        <v>425</v>
+      </c>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t>2019-09-10T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-19T05:23:15.024Z</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>WhisperX로 만드는 Voice → Text AI 노트 풀스택 웹앱: 결제 시스템으로 수익화까지</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>닭강정</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>39600</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>66000</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>AI 기술, 개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>자연어 처리, 웹 개발, 풀스택</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>saas, whisper, gemini, payments, Python, Kaggle, Express</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T05:00:30.000Z</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14T10:57:49.666Z</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/full-stack-voice-tex</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>컴맹도 따라하는 주식 바이브코딩 - AI로 만드는 주식 자동매매 시스템</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>얄팍한 코딩사전</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>154000</v>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>154000</v>
+      </c>
+      <c r="F73" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>671</v>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>AI 개발 활용, AI 실무 활용, AI 시작하기</t>
+        </is>
+      </c>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t>gemini, 인공지능(AI), CursorAI, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N73" s="7" t="n">
+        <v>461</v>
+      </c>
+      <c r="O73" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-06T06:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14T23:26:01.663Z</t>
+        </is>
+      </c>
+      <c r="Q73" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R73" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/stock-vibe-coding-ev</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>엑셀로 파해치는 인공지능 (AI with Excel)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>멋진</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>AI 기술</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>딥러닝 · 머신러닝</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>Python, Excel, 인공지능(AI)</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T04:30:05.000Z</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19T01:38:44.369Z</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/exploring-artificial</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>[취업폭격기] 사기업 IT취업 치트키 : 서류·포트폴리오·커리어까지 한 번에 뚫는 정규과정</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>취업폭격기</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>23100</v>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>77000</v>
+      </c>
+      <c r="F75" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>커리어 · 자기계발, 보안 · 네트워크, 개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>취업 · 이직, 보안 · 네트워크 기타, 개발 · 프로그래밍 기타</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>이력서, 기술면접, 자기계발, 취업</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="n">
+        <v>335</v>
+      </c>
+      <c r="O75" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13T14:30:04.000Z</t>
+        </is>
+      </c>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13T12:44:58.088Z</t>
+        </is>
+      </c>
+      <c r="Q75" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/job-bomber-private-s</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>자바 ORM 표준 JPA 프로그래밍 - 기본편</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>121000</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>2130</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>25406</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>백엔드, 웹 개발, 데이터베이스</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>Java, JPA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>963</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>2019-06-25T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-29T09:40:24.471Z</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/ORM-JPA-Basic</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Spotfire 응용편 - 반도체</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>피앤디솔루션</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>84700</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>84700</v>
+      </c>
+      <c r="F77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>데이터 사이언스</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>데이터 분석, 데이터 엔지니어링, 데이터 사이언스 기타</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>Spotfire</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="n">
+        <v>124</v>
+      </c>
+      <c r="O77" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-06T04:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-05T04:03:57.853Z</t>
+        </is>
+      </c>
+      <c r="Q77" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/spotfire-advanced-ap</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>알고런 데이터코드 연구소</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>79200</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>79200</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>데이터 사이언스</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>785</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-07T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T07:40:07.999Z</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>[Rookiss] 클로드 하네스 입문 (인터랙티브 교재)</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Rookiss</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>69300</v>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F79" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>AI 기술, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, AI 개발 활용, AI 시작하기</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t>Python, 인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N79" s="7" t="n">
+        <v>197</v>
+      </c>
+      <c r="O79" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-24T09:30:06.000Z</t>
+        </is>
+      </c>
+      <c r="P79" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23T12:07:23.052Z</t>
+        </is>
+      </c>
+      <c r="Q79" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/rookiss-introduction-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>강민철</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>5737</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>보안 · 네트워크</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>네트워크, tcpip, routing</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>779</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-14T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-29T09:27:31.006Z</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>퇴근후딴짓</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>121000</v>
+      </c>
+      <c r="F81" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>915</v>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>5725</v>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>데이터 사이언스</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>데이터 사이언스 자격증, 데이터 분석</t>
+        </is>
+      </c>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="n">
+        <v>1503</v>
+      </c>
+      <c r="O81" s="7" t="inlineStr">
+        <is>
+          <t>2022-12-12T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P81" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-13T14:45:20.463Z</t>
+        </is>
+      </c>
+      <c r="Q81" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>스프링 MVC 1편 - 백엔드 웹 개발 핵심 기술</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>99000</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>2585</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>30981</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>백엔드, 웹 개발</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>MVC, Spring</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>923</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>2021-03-06T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-29T07:20:11.745Z</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/스프링-mvc-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>토스페이먼츠 완벽 가이드: 슬라이드로 이해하는 결제 연동</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>온코딩</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>24200</v>
+      </c>
+      <c r="F83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 기획 · 경영 · 마케팅</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>백엔드, 웹 개발, 기획 · PM· PO</t>
+        </is>
+      </c>
+      <c r="M83" s="7" t="inlineStr">
+        <is>
+          <t>api, github-webhook, payments</t>
+        </is>
+      </c>
+      <c r="N83" s="7" t="n">
+        <v>501</v>
+      </c>
+      <c r="O83" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07T10:01:02.000Z</t>
+        </is>
+      </c>
+      <c r="P83" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07T08:01:07.455Z</t>
+        </is>
+      </c>
+      <c r="Q83" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/the-ultimate-guide-t-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>초보자도 따라하는 클로드코드 한방에 해결하기 - 클로드 코드 마스터 저자직강 입문자용</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>코드빌런</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>96800</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>96800</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>PostgreSQL, cloudflare, vercel, 프롬프트엔지니어링, AI Agent, claude, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>495</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T09:00:06.000Z</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T14:45:57.913Z</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/solving-claude-code</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>독하게 시작하는 C 프로그래밍</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>널널한 개발자</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>99000</v>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F85" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H85" s="7" t="n">
+        <v>234</v>
+      </c>
+      <c r="I85" s="7" t="n">
+        <v>3042</v>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+        </is>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>프로그래밍 언어, 시스템 · 운영체제</t>
+        </is>
+      </c>
+      <c r="M85" s="7" t="inlineStr">
+        <is>
+          <t>C, 컴퓨터 구조, assembly-language, vc++</t>
+        </is>
+      </c>
+      <c r="N85" s="7" t="n">
+        <v>1739</v>
+      </c>
+      <c r="O85" s="7" t="inlineStr">
+        <is>
+          <t>2023-09-26T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P85" s="7" t="inlineStr">
+        <is>
+          <t>2025-05-13T07:29:20.937Z</t>
+        </is>
+      </c>
+      <c r="Q85" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/독하게-시작하는-c프로그래밍</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>SQLD의 정석: 노랭이 문제집 씹어먹기</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>정미나</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>데이터 분석, 개발 · 프로그래밍 자격증</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>SQLD, SQL, Oracle, MSSQL</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-13T09:30:00.000Z</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16T02:31:26.559Z</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/sqld의-정석-노랭이-문제집-씹어먹</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>디지털포렌식전문가 2급 필기 핵심 요약집[전자책]</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>훈지손</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>38500</v>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>38500</v>
+      </c>
+      <c r="F87" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="I87" s="7" t="n">
+        <v>1228</v>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>보안 · 네트워크</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>보안, 보안 · 네트워크 자격증</t>
+        </is>
+      </c>
+      <c r="M87" s="7" t="inlineStr">
+        <is>
+          <t>Forensic</t>
+        </is>
+      </c>
+      <c r="N87" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O87" s="7" t="inlineStr">
+        <is>
+          <t>2023-02-16T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P87" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-05T15:57:52.306Z</t>
+        </is>
+      </c>
+      <c r="Q87" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/디지털포렌식전문가-2급-필기-전자책</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>MATLAB/Simulink 자동차 MBD 실무 입문: 모델링부터 검증과 코드 생성까지</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>제어쟁이</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>90860</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>129800</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>모빌리티, 임베디드 · IoT</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>MATLAB</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T10:30:05.000Z</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19T07:45:28.669Z</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/introduction-to-prac</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>LLM을 활용한 실시간 SQL생성(Text-To-SQL)</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>bradkim</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>23100</v>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>33000</v>
+      </c>
+      <c r="F89" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>AI 기술, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발, 인공지능 기타, AI 개발 활용</t>
+        </is>
+      </c>
+      <c r="M89" s="7" t="inlineStr">
+        <is>
+          <t>Python, 챗봇, FastAPI, workflow, 인공지능(AI), LLM, openAI API</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="n">
+        <v>196</v>
+      </c>
+      <c r="O89" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20T04:30:05.000Z</t>
+        </is>
+      </c>
+      <c r="P89" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20T06:39:33.938Z</t>
+        </is>
+      </c>
+      <c r="Q89" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/real-time-sql-genera</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>김영한의 실전 데이터베이스 - 설계 1편, 현대적 데이터 모델링 완전 정복</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>김영한</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>99000</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>3716</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>972</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-15T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09T09:36:10.311Z</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계1편</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Rookiss</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>128700</v>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>128700</v>
+      </c>
+      <c r="F91" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H91" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I91" s="7" t="n">
+        <v>135</v>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>AI 활용(AX), 업무 생산성</t>
+        </is>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>AI 실무 활용, 오피스, 업무 자동화</t>
+        </is>
+      </c>
+      <c r="M91" s="7" t="inlineStr">
+        <is>
+          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
+        </is>
+      </c>
+      <c r="N91" s="7" t="n">
+        <v>806</v>
+      </c>
+      <c r="O91" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-05T16:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P91" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-18T04:29:40.792Z</t>
+        </is>
+      </c>
+      <c r="Q91" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/starting-with-claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>AI 기반 아날로그/디지털 회로설계 자동화 실무 - 현업 LDO/AXI-Lite IP 설계와 검증</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>회로설계 멘토 삼코치</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>297000</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>297000</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>하드웨어, AI 활용(AX)</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>반도체, 임베디드 · IoT, AI 실무 활용</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>Python, system-verilog, uvm, batch-script, rtl</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>1209</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-04T12:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22T14:32:44.331Z</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R92" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/ai-기반-아날로그디지털-회로설계-자</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>처음하는 파이썬 백엔드 FastAPI 입문 (FastAPI부터 비동기 SQLAlchemy까지) [풀스택 Part1-2]</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>잔재미코딩 DaveLee</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>77000</v>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>77000</v>
+      </c>
+      <c r="F93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H93" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="I93" s="7" t="n">
+        <v>914</v>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>백엔드, 풀스택, 웹 개발</t>
+        </is>
+      </c>
+      <c r="M93" s="7" t="inlineStr">
+        <is>
+          <t>FastAPI, Python, backend, MVC, SQLAlchemy</t>
+        </is>
+      </c>
+      <c r="N93" s="7" t="n">
+        <v>775</v>
+      </c>
+      <c r="O93" s="7" t="inlineStr">
+        <is>
+          <t>2024-03-11T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P93" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-29T09:54:25.034Z</t>
+        </is>
+      </c>
+      <c r="Q93" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R93" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/파이썬-백엔드-fastapi-부트캠프</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>생성형 AI로 만드는 맞춤형 교육 플랫폼: AI Tutor부터 진로상담 시스템까지</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>HJ 데이터 아카데미</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>26070</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>86900</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>AI 활용(AX), AI 기술, 데이터 사이언스</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>AI 실무 활용, AI에이전트 개발, 데이터 분석</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>온라인 교육, colab, visualisation, Midjourney, 프롬프트엔지니어링</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T03:30:05.000Z</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T13:41:50.727Z</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R94" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/personalized-educati</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>실전에서 바로 써먹는 Kafka 입문</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>JSCODE 박재성</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>88000</v>
+      </c>
+      <c r="F95" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G95" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H95" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="I95" s="7" t="n">
+        <v>736</v>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>백엔드, 데브옵스 · 인프라, 클라우드</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>Kafka, EDA, MSA, devops, infrastructure</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="n">
+        <v>314</v>
+      </c>
+      <c r="O95" s="7" t="inlineStr">
+        <is>
+          <t>2025-07-28T06:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P95" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-11T05:22:53.951Z</t>
+        </is>
+      </c>
+      <c r="Q95" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R95" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/실전에서-바로-써먹는-kafka-입문</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>입문자를 위한 LangChain 기초 — v1.0+ 업데이트</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>판다스 스튜디오</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>446</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>6398</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>AI 기술</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>AI에이전트 개발</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Python, LLM, LangChain, RAG, AI Agent</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-17T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04T02:57:10.249Z</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R96" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/입문자를위한-랭체인-기초</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>"AI 딸깍의 시대" 원리로 돌파하는 Node.js와 CS Part 4 - HTTP 심연과 커스텀 프레임워크</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>nhcodingstudio</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>36300</v>
+      </c>
+      <c r="E97" s="9" t="n">
+        <v>121000</v>
+      </c>
+      <c r="F97" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="7" t="n">
+        <v>139</v>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>풀스택, 웹 개발, 백엔드</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>JavaScript, Node.js, 컴퓨터 구조, 인공지능(AI), React, frontend, backend</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="n">
+        <v>433</v>
+      </c>
+      <c r="O97" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-28T18:00:05.000Z</t>
+        </is>
+      </c>
+      <c r="P97" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-28T13:50:52.311Z</t>
+        </is>
+      </c>
+      <c r="Q97" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R97" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/nodejs-and-cs-part-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>빅데이터분석기사 필기 올인원: 3주에 끝내는 완벽 대비</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Masocampus</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>159500</v>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>159500</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>387</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>데이터 사이언스</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>데이터 사이언스 자격증</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>빅데이터분석기사, 빅데이터, 통계, 인공지능(AI)</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>1955</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-15T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-19T05:09:22.115Z</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R98" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/빅데이터분서기사-필기-올인원-3주완성</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Spotfire - 사용자 교육 기초편</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>피앤디솔루션</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>49500</v>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>49500</v>
+      </c>
+      <c r="F99" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H99" s="7" t="n">
+        <v>147</v>
+      </c>
+      <c r="I99" s="7" t="n">
+        <v>1089</v>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>데이터 사이언스</t>
+        </is>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>데이터 분석</t>
+        </is>
+      </c>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>Spotfire</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="n">
+        <v>270</v>
+      </c>
+      <c r="O99" s="7" t="inlineStr">
+        <is>
+          <t>2021-01-06T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P99" s="7" t="inlineStr">
+        <is>
+          <t>2025-05-13T07:50:03.402Z</t>
+        </is>
+      </c>
+      <c r="Q99" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R99" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/spotfire-기초</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>실리콘밸리 엔지니어와 함께하는 Docker</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>미쿡엔지니어</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>4146</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>개발 · 프로그래밍</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>데브옵스 · 인프라</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>Docker, container</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-23T15:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-19T03:27:19.991Z</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R100" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/실리콘밸리-엔지니어-도커</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>영어 말하기 입문 4주 완성 - 반응 속도 훈련</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>김병국(프랭크2024)</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F101" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>AI 활용(AX), 커리어 · 자기계발, 외국어</t>
+        </is>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>AI 실무 활용, 개인 브랜딩, 영어</t>
+        </is>
+      </c>
+      <c r="M101" s="7" t="inlineStr">
+        <is>
+          <t>프레젠테이션, 영어, 스피치, reflection, patterns</t>
+        </is>
+      </c>
+      <c r="N101" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O101" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-22T15:30:05.000Z</t>
+        </is>
+      </c>
+      <c r="P101" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-22T13:46:25.171Z</t>
+        </is>
+      </c>
+      <c r="Q101" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:43:30+09:00</t>
+        </is>
+      </c>
+      <c r="R101" s="6" t="inlineStr">
+        <is>
+          <t>https://www.inflearn.com/course/4-week-english-speak</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R11"/>
+  <autoFilter ref="A1:R101"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId2"/>
@@ -1372,6 +8206,96 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R101" r:id="rId100"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1410,7 +8334,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/ko/</t>
+          <t>https://www.inflearn.com/courses</t>
         </is>
       </c>
     </row>
@@ -1422,7 +8346,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-25T08:36:29+09:00</t>
+          <t>2026-07-25T08:43:30+09:00</t>
         </is>
       </c>
     </row>
@@ -1433,7 +8357,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">

--- a/inflearn/output/inflearn_main_2026-07-25.xlsx
+++ b/inflearn/output/inflearn_main_2026-07-25.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-25T08:43:30+09:00</t>
+          <t>2026-07-25T08:45:46+09:00</t>
         </is>
       </c>
     </row>

--- a/inflearn/output/inflearn_main_2026-07-25.xlsx
+++ b/inflearn/output/inflearn_main_2026-07-25.xlsx
@@ -629,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -781,7 +781,7 @@
         <v>6</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -857,7 +857,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -930,10 +930,10 @@
         <v>4.9</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9772</v>
+        <v>9773</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
@@ -1009,7 +1009,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -1085,7 +1085,7 @@
         <v>424</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>9821</v>
+        <v>9830</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -1161,7 +1161,7 @@
         <v>4</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -1389,7 +1389,7 @@
         <v>60</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
@@ -1617,7 +1617,7 @@
         <v>154</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>2560</v>
+        <v>2563</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
@@ -1766,7 +1766,7 @@
         <v>4.9</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>933</v>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -1997,7 +1997,7 @@
         <v>3020</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>56419</v>
+        <v>56421</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
@@ -2073,7 +2073,7 @@
         <v>317</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>3488</v>
+        <v>3491</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
@@ -2144,7 +2144,7 @@
         <v>4.7</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>1031</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
@@ -2220,7 +2220,7 @@
         <v>5</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>7996</v>
+        <v>7997</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>122422</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -2603,7 +2603,7 @@
         <v>49</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -2829,7 +2829,7 @@
         <v>1511</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>15228</v>
+        <v>15229</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -2902,7 +2902,7 @@
         <v>5</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>10654</v>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -3133,7 +3133,7 @@
         <v>23</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -3589,7 +3589,7 @@
         <v>2</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
@@ -3665,7 +3665,7 @@
         <v>1878</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>39448</v>
+        <v>39450</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -3741,7 +3741,7 @@
         <v>675</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>10825</v>
+        <v>10826</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
@@ -4273,7 +4273,7 @@
         <v>71</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -4653,7 +4653,7 @@
         <v>65</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
@@ -5033,7 +5033,7 @@
         <v>440</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>20666</v>
+        <v>20667</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
@@ -5413,7 +5413,7 @@
         <v>26</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
@@ -5565,7 +5565,7 @@
         <v>16</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
@@ -5639,7 +5639,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -6171,7 +6171,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
@@ -6475,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
@@ -6551,7 +6551,7 @@
         <v>174</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>5737</v>
+        <v>5739</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
@@ -6855,7 +6855,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
@@ -7767,7 +7767,7 @@
         <v>446</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>6398</v>
+        <v>6399</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
@@ -8071,7 +8071,7 @@
         <v>291</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>4146</v>
+        <v>4147</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-25T08:45:46+09:00</t>
+          <t>2026-07-25T12:39:18+09:00</t>
         </is>
       </c>
     </row>
